--- a/data/regime_variables/inflation/Eurozone_PPI.xlsx
+++ b/data/regime_variables/inflation/Eurozone_PPI.xlsx
@@ -1,34 +1,139 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidadfv-my.sharepoint.com/personal/9203718_alumnos_ufv_es/Documents/BAINF/PAPER/data/regime_variables/inflation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_44770E733365FFB87A4172D9CCB4CA3E97241AA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F480975-2D2C-4648-ADF1-BB536CDE1ADD}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Historical Values" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+  <si>
+    <t>Economic Indicator</t>
+  </si>
+  <si>
+    <t>Euro Zone</t>
+  </si>
+  <si>
+    <t>Domestic Producer Prices, MIG_CAG, Capital goods (EA21), Index, 2021=100</t>
+  </si>
+  <si>
+    <t>Time Span:</t>
+  </si>
+  <si>
+    <t>Jan 1995 to Feb 2026, Monthly</t>
+  </si>
+  <si>
+    <t>Adjustment:</t>
+  </si>
+  <si>
+    <t>Price index, not seasonally adjusted</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Eurostat</t>
+  </si>
+  <si>
+    <t>Last Updated:</t>
+  </si>
+  <si>
+    <t>8 Apr 2026</t>
+  </si>
+  <si>
+    <t>Actual(Feb 2026):</t>
+  </si>
+  <si>
+    <t>117.5</t>
+  </si>
+  <si>
+    <t>Prior:</t>
+  </si>
+  <si>
+    <t>117.2</t>
+  </si>
+  <si>
+    <t>Press Release:</t>
+  </si>
+  <si>
+    <t>https://ec.europa.eu/eurostat/en/web/products-euro-indicators/w/4-08042026-ap</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>Euro Zone Domestic Producer Prices, MIG_CAG, Capital goods (EA21), Index, 2021=100</t>
+  </si>
+  <si>
+    <t>Download Date</t>
+  </si>
+  <si>
+    <t>24 Apr 2026</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Actual (Revised)</t>
+  </si>
+  <si>
+    <t>aXZPPIC</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="12"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Tahoma"/>
       <b/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Tahoma"/>
-      <b/>
     </font>
     <font>
       <sz val="8"/>
@@ -39,59 +144,46 @@
       <name val="Tahoma"/>
     </font>
     <font>
+      <b/>
       <sz val="8"/>
       <name val="Tahoma"/>
-      <b/>
     </font>
     <font>
+      <b/>
       <sz val="8"/>
       <name val="Tahoma"/>
-      <b/>
     </font>
     <font>
+      <b/>
       <sz val="8"/>
       <name val="Tahoma"/>
-      <b/>
     </font>
     <font>
+      <b/>
       <sz val="8"/>
+      <color rgb="FFFF9933"/>
       <name val="Tahoma"/>
-      <b/>
-      <color rgb="FF9933"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2E2E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E2E2"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -130,31 +222,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -479,153 +582,3519 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H390"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="16" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Economic Indicator</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>Euro Zone</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Domestic Producer Prices, MIG_CAG, Capital goods (EA21), Index, 2021=100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="str">
-        <v>Time Span:</v>
-      </c>
-      <c r="B5" s="6" t="str">
-        <v>Jan 1995 to Feb 2026, Monthly</v>
-      </c>
-      <c r="C5" s="6" t="str">
-        <v>Adjustment:</v>
-      </c>
-      <c r="D5" s="6" t="str">
-        <v>Price index, not seasonally adjusted</v>
-      </c>
-      <c r="E5" s="6" t="str">
-        <v>Source:</v>
-      </c>
-      <c r="F5" s="6" t="str">
-        <v>Eurostat</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="str">
-        <v>Last Updated:</v>
-      </c>
-      <c r="B6" s="6" t="str">
-        <v>8 Apr 2026</v>
-      </c>
-      <c r="C6" s="7" t="str">
-        <v>Actual(Feb 2026):</v>
-      </c>
-      <c r="D6" s="7" t="str">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="10" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46081</v>
+      </c>
+      <c r="B17">
         <v>117.5</v>
       </c>
-      <c r="E6" s="6" t="str">
-        <v>Prior:</v>
-      </c>
-      <c r="F6" s="6" t="str">
-        <v>117.2</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <v>Press Release:</v>
-      </c>
-      <c r="H6" s="6" t="str">
-        <v>https://ec.europa.eu/eurostat/en/web/products-euro-indicators/w/4-08042026-ap</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="str">
-        <v>Indicator</v>
-      </c>
-      <c r="B9" s="8" t="str">
-        <v>Euro Zone Domestic Producer Prices, MIG_CAG, Capital goods (EA21), Index, 2021=100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="str">
-        <v>Download Date</v>
-      </c>
-      <c r="B10" s="8" t="str">
-        <v>24 Apr 2026</v>
-      </c>
-      <c r="C10" s="8" t="str">
-        <f>=@RDP.HistoricalPricing($B$16:$B$16,"VALUE"," START:31-Jan-1995 END:28-Feb-2026 INTERVAL:P1M SOURCE:RFV",,"TSREPEAT:NO RH:TimeStamp",$A$17)</f>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="str">
-        <v>Unit</v>
-      </c>
-      <c r="B11" s="8" t="str">
-        <v>Index</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="str">
-        <v>Period</v>
-      </c>
-      <c r="B14" s="10" t="str">
-        <v>Actual (Revised)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="str">
-        <v>Period</v>
-      </c>
-      <c r="B15" s="10" t="str">
-        <v>Actual (Revised)</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="str">
-        <v>Period</v>
-      </c>
-      <c r="B16" s="10" t="str">
-        <v>aXZPPIC</v>
-      </c>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>46053</v>
+      </c>
+      <c r="B18">
+        <v>117.3</v>
+      </c>
+      <c r="D18" s="11"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>46022</v>
+      </c>
+      <c r="B19">
+        <v>116.5</v>
+      </c>
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>45991</v>
+      </c>
+      <c r="B20">
+        <v>116.5</v>
+      </c>
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="11">
+        <v>45961</v>
+      </c>
+      <c r="B21">
+        <v>116.3</v>
+      </c>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
+        <v>45930</v>
+      </c>
+      <c r="B22">
+        <v>116.2</v>
+      </c>
+      <c r="D22" s="11"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="11">
+        <v>45900</v>
+      </c>
+      <c r="B23">
+        <v>116.2</v>
+      </c>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="11">
+        <v>45869</v>
+      </c>
+      <c r="B24">
+        <v>116.1</v>
+      </c>
+      <c r="D24" s="11"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="11">
+        <v>45838</v>
+      </c>
+      <c r="B25">
+        <v>116.1</v>
+      </c>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="11">
+        <v>45808</v>
+      </c>
+      <c r="B26">
+        <v>115.9</v>
+      </c>
+      <c r="D26" s="11"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="11">
+        <v>45777</v>
+      </c>
+      <c r="B27">
+        <v>115.8</v>
+      </c>
+      <c r="D27" s="11"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="11">
+        <v>45747</v>
+      </c>
+      <c r="B28">
+        <v>115.8</v>
+      </c>
+      <c r="D28" s="11"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="11">
+        <v>45716</v>
+      </c>
+      <c r="B29">
+        <v>115.6</v>
+      </c>
+      <c r="D29" s="11"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="11">
+        <v>45688</v>
+      </c>
+      <c r="B30">
+        <v>115.4</v>
+      </c>
+      <c r="D30" s="11"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="11">
+        <v>45657</v>
+      </c>
+      <c r="B31">
+        <v>114.5</v>
+      </c>
+      <c r="D31" s="11"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="11">
+        <v>45626</v>
+      </c>
+      <c r="B32">
+        <v>114.4</v>
+      </c>
+      <c r="D32" s="11"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="11">
+        <v>45596</v>
+      </c>
+      <c r="B33">
+        <v>114.4</v>
+      </c>
+      <c r="D33" s="11"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="11">
+        <v>45565</v>
+      </c>
+      <c r="B34">
+        <v>114.2</v>
+      </c>
+      <c r="D34" s="11"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="11">
+        <v>45535</v>
+      </c>
+      <c r="B35">
+        <v>114.3</v>
+      </c>
+      <c r="D35" s="11"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="11">
+        <v>45504</v>
+      </c>
+      <c r="B36">
+        <v>114.1</v>
+      </c>
+      <c r="D36" s="11"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="11">
+        <v>45473</v>
+      </c>
+      <c r="B37">
+        <v>114.1</v>
+      </c>
+      <c r="D37" s="11"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="11">
+        <v>45443</v>
+      </c>
+      <c r="B38">
+        <v>114</v>
+      </c>
+      <c r="D38" s="11"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="11">
+        <v>45412</v>
+      </c>
+      <c r="B39">
+        <v>113.9</v>
+      </c>
+      <c r="D39" s="11"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="11">
+        <v>45382</v>
+      </c>
+      <c r="B40">
+        <v>113.8</v>
+      </c>
+      <c r="D40" s="11"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="11">
+        <v>45351</v>
+      </c>
+      <c r="B41">
+        <v>113.7</v>
+      </c>
+      <c r="D41" s="11"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="11">
+        <v>45322</v>
+      </c>
+      <c r="B42">
+        <v>113.5</v>
+      </c>
+      <c r="D42" s="11"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="11">
+        <v>45291</v>
+      </c>
+      <c r="B43">
+        <v>112.8</v>
+      </c>
+      <c r="D43" s="11"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="11">
+        <v>45260</v>
+      </c>
+      <c r="B44">
+        <v>112.7</v>
+      </c>
+      <c r="D44" s="11"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="11">
+        <v>45230</v>
+      </c>
+      <c r="B45">
+        <v>112.8</v>
+      </c>
+      <c r="D45" s="11"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="11">
+        <v>45199</v>
+      </c>
+      <c r="B46">
+        <v>112.8</v>
+      </c>
+      <c r="D46" s="11"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="11">
+        <v>45169</v>
+      </c>
+      <c r="B47">
+        <v>112.7</v>
+      </c>
+      <c r="D47" s="11"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="11">
+        <v>45138</v>
+      </c>
+      <c r="B48">
+        <v>112.6</v>
+      </c>
+      <c r="D48" s="11"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="11">
+        <v>45107</v>
+      </c>
+      <c r="B49">
+        <v>112.3</v>
+      </c>
+      <c r="D49" s="11"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="11">
+        <v>45077</v>
+      </c>
+      <c r="B50">
+        <v>112.2</v>
+      </c>
+      <c r="D50" s="11"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="11">
+        <v>45046</v>
+      </c>
+      <c r="B51">
+        <v>112.1</v>
+      </c>
+      <c r="D51" s="11"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="11">
+        <v>45016</v>
+      </c>
+      <c r="B52">
+        <v>111.6</v>
+      </c>
+      <c r="D52" s="11"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="11">
+        <v>44985</v>
+      </c>
+      <c r="B53">
+        <v>111.4</v>
+      </c>
+      <c r="D53" s="11"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="11">
+        <v>44957</v>
+      </c>
+      <c r="B54">
+        <v>111</v>
+      </c>
+      <c r="D54" s="11"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="11">
+        <v>44926</v>
+      </c>
+      <c r="B55">
+        <v>109.4</v>
+      </c>
+      <c r="D55" s="11"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
+        <v>44895</v>
+      </c>
+      <c r="B56">
+        <v>109.3</v>
+      </c>
+      <c r="D56" s="11"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="11">
+        <v>44865</v>
+      </c>
+      <c r="B57">
+        <v>109</v>
+      </c>
+      <c r="D57" s="11"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
+        <v>44834</v>
+      </c>
+      <c r="B58">
+        <v>108.7</v>
+      </c>
+      <c r="D58" s="11"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="11">
+        <v>44804</v>
+      </c>
+      <c r="B59">
+        <v>108.3</v>
+      </c>
+      <c r="D59" s="11"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
+        <v>44773</v>
+      </c>
+      <c r="B60">
+        <v>107.8</v>
+      </c>
+      <c r="D60" s="11"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="11">
+        <v>44742</v>
+      </c>
+      <c r="B61">
+        <v>107</v>
+      </c>
+      <c r="D61" s="11"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="11">
+        <v>44712</v>
+      </c>
+      <c r="B62">
+        <v>106.6</v>
+      </c>
+      <c r="D62" s="11"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="11">
+        <v>44681</v>
+      </c>
+      <c r="B63">
+        <v>106</v>
+      </c>
+      <c r="D63" s="11"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="11">
+        <v>44651</v>
+      </c>
+      <c r="B64">
+        <v>105</v>
+      </c>
+      <c r="D64" s="11"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="11">
+        <v>44620</v>
+      </c>
+      <c r="B65">
+        <v>104.2</v>
+      </c>
+      <c r="D65" s="11"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="11">
+        <v>44592</v>
+      </c>
+      <c r="B66">
+        <v>103.7</v>
+      </c>
+      <c r="D66" s="11"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="11">
+        <v>44561</v>
+      </c>
+      <c r="B67">
+        <v>102.2</v>
+      </c>
+      <c r="D67" s="11"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="11">
+        <v>44530</v>
+      </c>
+      <c r="B68">
+        <v>101.9</v>
+      </c>
+      <c r="D68" s="11"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="11">
+        <v>44500</v>
+      </c>
+      <c r="B69">
+        <v>101.5</v>
+      </c>
+      <c r="D69" s="11"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="11">
+        <v>44469</v>
+      </c>
+      <c r="B70">
+        <v>101</v>
+      </c>
+      <c r="D70" s="11"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="11">
+        <v>44439</v>
+      </c>
+      <c r="B71">
+        <v>100.5</v>
+      </c>
+      <c r="D71" s="11"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="11">
+        <v>44408</v>
+      </c>
+      <c r="B72">
+        <v>100.1</v>
+      </c>
+      <c r="D72" s="11"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="11">
+        <v>44377</v>
+      </c>
+      <c r="B73">
+        <v>99.6</v>
+      </c>
+      <c r="D73" s="11"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="11">
+        <v>44347</v>
+      </c>
+      <c r="B74">
+        <v>99.2</v>
+      </c>
+      <c r="D74" s="11"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="11">
+        <v>44316</v>
+      </c>
+      <c r="B75">
+        <v>98.8</v>
+      </c>
+      <c r="D75" s="11"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="11">
+        <v>44286</v>
+      </c>
+      <c r="B76">
+        <v>98.6</v>
+      </c>
+      <c r="D76" s="11"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="11">
+        <v>44255</v>
+      </c>
+      <c r="B77">
+        <v>98.3</v>
+      </c>
+      <c r="D77" s="11"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="11">
+        <v>44227</v>
+      </c>
+      <c r="B78">
+        <v>98.2</v>
+      </c>
+      <c r="D78" s="11"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="11">
+        <v>44196</v>
+      </c>
+      <c r="B79">
+        <v>97.7</v>
+      </c>
+      <c r="D79" s="11"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="11">
+        <v>44165</v>
+      </c>
+      <c r="B80">
+        <v>97.6</v>
+      </c>
+      <c r="D80" s="11"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="11">
+        <v>44135</v>
+      </c>
+      <c r="B81">
+        <v>97.6</v>
+      </c>
+      <c r="D81" s="11"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="11">
+        <v>44104</v>
+      </c>
+      <c r="B82">
+        <v>97.6</v>
+      </c>
+      <c r="D82" s="11"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="11">
+        <v>44074</v>
+      </c>
+      <c r="B83">
+        <v>97.5</v>
+      </c>
+      <c r="D83" s="11"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="11">
+        <v>44043</v>
+      </c>
+      <c r="B84">
+        <v>97.6</v>
+      </c>
+      <c r="D84" s="11"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="11">
+        <v>44012</v>
+      </c>
+      <c r="B85">
+        <v>97.6</v>
+      </c>
+      <c r="D85" s="11"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="11">
+        <v>43982</v>
+      </c>
+      <c r="B86">
+        <v>97.4</v>
+      </c>
+      <c r="D86" s="11"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="11">
+        <v>43951</v>
+      </c>
+      <c r="B87">
+        <v>97.5</v>
+      </c>
+      <c r="D87" s="11"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="11">
+        <v>43921</v>
+      </c>
+      <c r="B88">
+        <v>97.4</v>
+      </c>
+      <c r="D88" s="11"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="11">
+        <v>43890</v>
+      </c>
+      <c r="B89">
+        <v>97.4</v>
+      </c>
+      <c r="D89" s="11"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="11">
+        <v>43861</v>
+      </c>
+      <c r="B90">
+        <v>97.3</v>
+      </c>
+      <c r="D90" s="11"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="11">
+        <v>43830</v>
+      </c>
+      <c r="B91">
+        <v>96.9</v>
+      </c>
+      <c r="D91" s="11"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="11">
+        <v>43799</v>
+      </c>
+      <c r="B92">
+        <v>96.9</v>
+      </c>
+      <c r="D92" s="11"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="11">
+        <v>43769</v>
+      </c>
+      <c r="B93">
+        <v>96.9</v>
+      </c>
+      <c r="D93" s="11"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="11">
+        <v>43738</v>
+      </c>
+      <c r="B94">
+        <v>96.8</v>
+      </c>
+      <c r="D94" s="11"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="11">
+        <v>43708</v>
+      </c>
+      <c r="B95">
+        <v>96.8</v>
+      </c>
+      <c r="D95" s="11"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="11">
+        <v>43677</v>
+      </c>
+      <c r="B96">
+        <v>96.8</v>
+      </c>
+      <c r="D96" s="11"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="11">
+        <v>43646</v>
+      </c>
+      <c r="B97">
+        <v>96.7</v>
+      </c>
+      <c r="D97" s="11"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="11">
+        <v>43616</v>
+      </c>
+      <c r="B98">
+        <v>96.6</v>
+      </c>
+      <c r="D98" s="11"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="11">
+        <v>43585</v>
+      </c>
+      <c r="B99">
+        <v>96.5</v>
+      </c>
+      <c r="D99" s="11"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="11">
+        <v>43555</v>
+      </c>
+      <c r="B100">
+        <v>96.4</v>
+      </c>
+      <c r="D100" s="11"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="11">
+        <v>43524</v>
+      </c>
+      <c r="B101">
+        <v>96.4</v>
+      </c>
+      <c r="D101" s="11"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="11">
+        <v>43496</v>
+      </c>
+      <c r="B102">
+        <v>96.3</v>
+      </c>
+      <c r="D102" s="11"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="11">
+        <v>43465</v>
+      </c>
+      <c r="B103">
+        <v>95.7</v>
+      </c>
+      <c r="D103" s="11"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="11">
+        <v>43434</v>
+      </c>
+      <c r="B104">
+        <v>95.7</v>
+      </c>
+      <c r="D104" s="11"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="11">
+        <v>43404</v>
+      </c>
+      <c r="B105">
+        <v>95.7</v>
+      </c>
+      <c r="D105" s="11"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="11">
+        <v>43373</v>
+      </c>
+      <c r="B106">
+        <v>95.5</v>
+      </c>
+      <c r="D106" s="11"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="11">
+        <v>43343</v>
+      </c>
+      <c r="B107">
+        <v>95.4</v>
+      </c>
+      <c r="D107" s="11"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="11">
+        <v>43312</v>
+      </c>
+      <c r="B108">
+        <v>95.4</v>
+      </c>
+      <c r="D108" s="11"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="11">
+        <v>43281</v>
+      </c>
+      <c r="B109">
+        <v>95.3</v>
+      </c>
+      <c r="D109" s="11"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="11">
+        <v>43251</v>
+      </c>
+      <c r="B110">
+        <v>95.2</v>
+      </c>
+      <c r="D110" s="11"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="11">
+        <v>43220</v>
+      </c>
+      <c r="B111">
+        <v>95.1</v>
+      </c>
+      <c r="D111" s="11"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="11">
+        <v>43190</v>
+      </c>
+      <c r="B112">
+        <v>95</v>
+      </c>
+      <c r="D112" s="11"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="11">
+        <v>43159</v>
+      </c>
+      <c r="B113">
+        <v>94.9</v>
+      </c>
+      <c r="D113" s="11"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="11">
+        <v>43131</v>
+      </c>
+      <c r="B114">
+        <v>94.8</v>
+      </c>
+      <c r="D114" s="11"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="11">
+        <v>43100</v>
+      </c>
+      <c r="B115">
+        <v>94.4</v>
+      </c>
+      <c r="D115" s="11"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="11">
+        <v>43069</v>
+      </c>
+      <c r="B116">
+        <v>94.4</v>
+      </c>
+      <c r="D116" s="11"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="11">
+        <v>43039</v>
+      </c>
+      <c r="B117">
+        <v>94.3</v>
+      </c>
+      <c r="D117" s="11"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="11">
+        <v>43008</v>
+      </c>
+      <c r="B118">
+        <v>94.2</v>
+      </c>
+      <c r="D118" s="11"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="11">
+        <v>42978</v>
+      </c>
+      <c r="B119">
+        <v>94.3</v>
+      </c>
+      <c r="D119" s="11"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="11">
+        <v>42947</v>
+      </c>
+      <c r="B120">
+        <v>94.2</v>
+      </c>
+      <c r="D120" s="11"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" s="11">
+        <v>42916</v>
+      </c>
+      <c r="B121">
+        <v>94.2</v>
+      </c>
+      <c r="D121" s="11"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" s="11">
+        <v>42886</v>
+      </c>
+      <c r="B122">
+        <v>94.1</v>
+      </c>
+      <c r="D122" s="11"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="11">
+        <v>42855</v>
+      </c>
+      <c r="B123">
+        <v>94.1</v>
+      </c>
+      <c r="D123" s="11"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="11">
+        <v>42825</v>
+      </c>
+      <c r="B124">
+        <v>94</v>
+      </c>
+      <c r="D124" s="11"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="11">
+        <v>42794</v>
+      </c>
+      <c r="B125">
+        <v>93.9</v>
+      </c>
+      <c r="D125" s="11"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
+        <v>42766</v>
+      </c>
+      <c r="B126">
+        <v>93.8</v>
+      </c>
+      <c r="D126" s="11"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
+        <v>42735</v>
+      </c>
+      <c r="B127">
+        <v>93.5</v>
+      </c>
+      <c r="D127" s="11"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
+        <v>42704</v>
+      </c>
+      <c r="B128">
+        <v>93.5</v>
+      </c>
+      <c r="D128" s="11"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
+        <v>42674</v>
+      </c>
+      <c r="B129">
+        <v>93.4</v>
+      </c>
+      <c r="D129" s="11"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
+        <v>42643</v>
+      </c>
+      <c r="B130">
+        <v>93.4</v>
+      </c>
+      <c r="D130" s="11"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
+        <v>42613</v>
+      </c>
+      <c r="B131">
+        <v>93.3</v>
+      </c>
+      <c r="D131" s="11"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
+        <v>42582</v>
+      </c>
+      <c r="B132">
+        <v>93.3</v>
+      </c>
+      <c r="D132" s="11"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
+        <v>42551</v>
+      </c>
+      <c r="B133">
+        <v>93.3</v>
+      </c>
+      <c r="D133" s="11"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
+        <v>42521</v>
+      </c>
+      <c r="B134">
+        <v>93.2</v>
+      </c>
+      <c r="D134" s="11"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
+        <v>42490</v>
+      </c>
+      <c r="B135">
+        <v>93.1</v>
+      </c>
+      <c r="D135" s="11"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
+        <v>42460</v>
+      </c>
+      <c r="B136">
+        <v>93</v>
+      </c>
+      <c r="D136" s="11"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
+        <v>42429</v>
+      </c>
+      <c r="B137">
+        <v>93</v>
+      </c>
+      <c r="D137" s="11"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
+        <v>42400</v>
+      </c>
+      <c r="B138">
+        <v>93</v>
+      </c>
+      <c r="D138" s="11"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
+        <v>42369</v>
+      </c>
+      <c r="B139">
+        <v>92.9</v>
+      </c>
+      <c r="D139" s="11"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
+        <v>42338</v>
+      </c>
+      <c r="B140">
+        <v>93</v>
+      </c>
+      <c r="D140" s="11"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
+        <v>42308</v>
+      </c>
+      <c r="B141">
+        <v>92.9</v>
+      </c>
+      <c r="D141" s="11"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
+        <v>42277</v>
+      </c>
+      <c r="B142">
+        <v>92.9</v>
+      </c>
+      <c r="D142" s="11"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
+        <v>42247</v>
+      </c>
+      <c r="B143">
+        <v>92.9</v>
+      </c>
+      <c r="D143" s="11"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
+        <v>42216</v>
+      </c>
+      <c r="B144">
+        <v>92.9</v>
+      </c>
+      <c r="D144" s="11"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
+        <v>42185</v>
+      </c>
+      <c r="B145">
+        <v>92.9</v>
+      </c>
+      <c r="D145" s="11"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
+        <v>42155</v>
+      </c>
+      <c r="B146">
+        <v>92.8</v>
+      </c>
+      <c r="D146" s="11"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
+        <v>42124</v>
+      </c>
+      <c r="B147">
+        <v>92.8</v>
+      </c>
+      <c r="D147" s="11"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
+        <v>42094</v>
+      </c>
+      <c r="B148">
+        <v>92.8</v>
+      </c>
+      <c r="D148" s="11"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
+        <v>42063</v>
+      </c>
+      <c r="B149">
+        <v>92.7</v>
+      </c>
+      <c r="D149" s="11"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
+        <v>42035</v>
+      </c>
+      <c r="B150">
+        <v>92.7</v>
+      </c>
+      <c r="D150" s="11"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="11">
+        <v>42004</v>
+      </c>
+      <c r="B151">
+        <v>92.5</v>
+      </c>
+      <c r="D151" s="11"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="11">
+        <v>41973</v>
+      </c>
+      <c r="B152">
+        <v>92.5</v>
+      </c>
+      <c r="D152" s="11"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="11">
+        <v>41943</v>
+      </c>
+      <c r="B153">
+        <v>92.4</v>
+      </c>
+      <c r="D153" s="11"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" s="11">
+        <v>41912</v>
+      </c>
+      <c r="B154">
+        <v>92.4</v>
+      </c>
+      <c r="D154" s="11"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" s="11">
+        <v>41882</v>
+      </c>
+      <c r="B155">
+        <v>92.3</v>
+      </c>
+      <c r="D155" s="11"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" s="11">
+        <v>41851</v>
+      </c>
+      <c r="B156">
+        <v>92.3</v>
+      </c>
+      <c r="D156" s="11"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" s="11">
+        <v>41820</v>
+      </c>
+      <c r="B157">
+        <v>92.2</v>
+      </c>
+      <c r="D157" s="11"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" s="11">
+        <v>41790</v>
+      </c>
+      <c r="B158">
+        <v>92.2</v>
+      </c>
+      <c r="D158" s="11"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" s="11">
+        <v>41759</v>
+      </c>
+      <c r="B159">
+        <v>92.1</v>
+      </c>
+      <c r="D159" s="11"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" s="11">
+        <v>41729</v>
+      </c>
+      <c r="B160">
+        <v>92.1</v>
+      </c>
+      <c r="D160" s="11"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" s="11">
+        <v>41698</v>
+      </c>
+      <c r="B161">
+        <v>92</v>
+      </c>
+      <c r="D161" s="11"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" s="11">
+        <v>41670</v>
+      </c>
+      <c r="B162">
+        <v>92</v>
+      </c>
+      <c r="D162" s="11"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" s="11">
+        <v>41639</v>
+      </c>
+      <c r="B163">
+        <v>91.8</v>
+      </c>
+      <c r="D163" s="11"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" s="11">
+        <v>41608</v>
+      </c>
+      <c r="B164">
+        <v>91.8</v>
+      </c>
+      <c r="D164" s="11"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" s="11">
+        <v>41578</v>
+      </c>
+      <c r="B165">
+        <v>91.8</v>
+      </c>
+      <c r="D165" s="11"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" s="11">
+        <v>41547</v>
+      </c>
+      <c r="B166">
+        <v>91.8</v>
+      </c>
+      <c r="D166" s="11"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" s="11">
+        <v>41517</v>
+      </c>
+      <c r="B167">
+        <v>91.9</v>
+      </c>
+      <c r="D167" s="11"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" s="11">
+        <v>41486</v>
+      </c>
+      <c r="B168">
+        <v>91.9</v>
+      </c>
+      <c r="D168" s="11"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" s="11">
+        <v>41455</v>
+      </c>
+      <c r="B169">
+        <v>91.8</v>
+      </c>
+      <c r="D169" s="11"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" s="11">
+        <v>41425</v>
+      </c>
+      <c r="B170">
+        <v>91.8</v>
+      </c>
+      <c r="D170" s="11"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" s="11">
+        <v>41394</v>
+      </c>
+      <c r="B171">
+        <v>91.9</v>
+      </c>
+      <c r="D171" s="11"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" s="11">
+        <v>41364</v>
+      </c>
+      <c r="B172">
+        <v>91.8</v>
+      </c>
+      <c r="D172" s="11"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" s="11">
+        <v>41333</v>
+      </c>
+      <c r="B173">
+        <v>91.8</v>
+      </c>
+      <c r="D173" s="11"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" s="11">
+        <v>41305</v>
+      </c>
+      <c r="B174">
+        <v>91.7</v>
+      </c>
+      <c r="D174" s="11"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" s="11">
+        <v>41274</v>
+      </c>
+      <c r="B175">
+        <v>91.4</v>
+      </c>
+      <c r="D175" s="11"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" s="11">
+        <v>41243</v>
+      </c>
+      <c r="B176">
+        <v>91.5</v>
+      </c>
+      <c r="D176" s="11"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="11">
+        <v>41213</v>
+      </c>
+      <c r="B177">
+        <v>91.5</v>
+      </c>
+      <c r="D177" s="11"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" s="11">
+        <v>41182</v>
+      </c>
+      <c r="B178">
+        <v>91.4</v>
+      </c>
+      <c r="D178" s="11"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" s="11">
+        <v>41152</v>
+      </c>
+      <c r="B179">
+        <v>91.5</v>
+      </c>
+      <c r="D179" s="11"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" s="11">
+        <v>41121</v>
+      </c>
+      <c r="B180">
+        <v>91.5</v>
+      </c>
+      <c r="D180" s="11"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" s="11">
+        <v>41090</v>
+      </c>
+      <c r="B181">
+        <v>91.5</v>
+      </c>
+      <c r="D181" s="11"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" s="11">
+        <v>41060</v>
+      </c>
+      <c r="B182">
+        <v>91.4</v>
+      </c>
+      <c r="D182" s="11"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" s="11">
+        <v>41029</v>
+      </c>
+      <c r="B183">
+        <v>91.4</v>
+      </c>
+      <c r="D183" s="11"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" s="11">
+        <v>40999</v>
+      </c>
+      <c r="B184">
+        <v>91.2</v>
+      </c>
+      <c r="D184" s="11"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" s="11">
+        <v>40968</v>
+      </c>
+      <c r="B185">
+        <v>91.1</v>
+      </c>
+      <c r="D185" s="11"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186" s="11">
+        <v>40939</v>
+      </c>
+      <c r="B186">
+        <v>91</v>
+      </c>
+      <c r="D186" s="11"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187" s="11">
+        <v>40908</v>
+      </c>
+      <c r="B187">
+        <v>90.8</v>
+      </c>
+      <c r="D187" s="11"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" s="11">
+        <v>40877</v>
+      </c>
+      <c r="B188">
+        <v>90.8</v>
+      </c>
+      <c r="D188" s="11"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" s="11">
+        <v>40847</v>
+      </c>
+      <c r="B189">
+        <v>90.8</v>
+      </c>
+      <c r="D189" s="11"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" s="11">
+        <v>40816</v>
+      </c>
+      <c r="B190">
+        <v>90.8</v>
+      </c>
+      <c r="D190" s="11"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" s="11">
+        <v>40786</v>
+      </c>
+      <c r="B191">
+        <v>90.8</v>
+      </c>
+      <c r="D191" s="11"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" s="11">
+        <v>40755</v>
+      </c>
+      <c r="B192">
+        <v>90.7</v>
+      </c>
+      <c r="D192" s="11"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" s="11">
+        <v>40724</v>
+      </c>
+      <c r="B193">
+        <v>90.6</v>
+      </c>
+      <c r="D193" s="11"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194" s="11">
+        <v>40694</v>
+      </c>
+      <c r="B194">
+        <v>90.5</v>
+      </c>
+      <c r="D194" s="11"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195" s="11">
+        <v>40663</v>
+      </c>
+      <c r="B195">
+        <v>90.5</v>
+      </c>
+      <c r="D195" s="11"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196" s="11">
+        <v>40633</v>
+      </c>
+      <c r="B196">
+        <v>90.3</v>
+      </c>
+      <c r="D196" s="11"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" s="11">
+        <v>40602</v>
+      </c>
+      <c r="B197">
+        <v>90.2</v>
+      </c>
+      <c r="D197" s="11"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198" s="11">
+        <v>40574</v>
+      </c>
+      <c r="B198">
+        <v>90</v>
+      </c>
+      <c r="D198" s="11"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" s="11">
+        <v>40543</v>
+      </c>
+      <c r="B199">
+        <v>89.6</v>
+      </c>
+      <c r="D199" s="11"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" s="11">
+        <v>40512</v>
+      </c>
+      <c r="B200">
+        <v>89.6</v>
+      </c>
+      <c r="D200" s="11"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" s="11">
+        <v>40482</v>
+      </c>
+      <c r="B201">
+        <v>89.5</v>
+      </c>
+      <c r="D201" s="11"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="11">
+        <v>40451</v>
+      </c>
+      <c r="B202">
+        <v>89.5</v>
+      </c>
+      <c r="D202" s="11"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203" s="11">
+        <v>40421</v>
+      </c>
+      <c r="B203">
+        <v>89.4</v>
+      </c>
+      <c r="D203" s="11"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204" s="11">
+        <v>40390</v>
+      </c>
+      <c r="B204">
+        <v>89.3</v>
+      </c>
+      <c r="D204" s="11"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A205" s="11">
+        <v>40359</v>
+      </c>
+      <c r="B205">
+        <v>89.3</v>
+      </c>
+      <c r="D205" s="11"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A206" s="11">
+        <v>40329</v>
+      </c>
+      <c r="B206">
+        <v>89.2</v>
+      </c>
+      <c r="D206" s="11"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A207" s="11">
+        <v>40298</v>
+      </c>
+      <c r="B207">
+        <v>89.1</v>
+      </c>
+      <c r="D207" s="11"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A208" s="11">
+        <v>40268</v>
+      </c>
+      <c r="B208">
+        <v>89</v>
+      </c>
+      <c r="D208" s="11"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A209" s="11">
+        <v>40237</v>
+      </c>
+      <c r="B209">
+        <v>88.9</v>
+      </c>
+      <c r="D209" s="11"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A210" s="11">
+        <v>40209</v>
+      </c>
+      <c r="B210">
+        <v>88.9</v>
+      </c>
+      <c r="D210" s="11"/>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A211" s="11">
+        <v>40178</v>
+      </c>
+      <c r="B211">
+        <v>88.9</v>
+      </c>
+      <c r="D211" s="11"/>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A212" s="11">
+        <v>40147</v>
+      </c>
+      <c r="B212">
+        <v>88.9</v>
+      </c>
+      <c r="D212" s="11"/>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A213" s="11">
+        <v>40117</v>
+      </c>
+      <c r="B213">
+        <v>89</v>
+      </c>
+      <c r="D213" s="11"/>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A214" s="11">
+        <v>40086</v>
+      </c>
+      <c r="B214">
+        <v>88.9</v>
+      </c>
+      <c r="D214" s="11"/>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A215" s="11">
+        <v>40056</v>
+      </c>
+      <c r="B215">
+        <v>89</v>
+      </c>
+      <c r="D215" s="11"/>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A216" s="11">
+        <v>40025</v>
+      </c>
+      <c r="B216">
+        <v>88.9</v>
+      </c>
+      <c r="D216" s="11"/>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A217" s="11">
+        <v>39994</v>
+      </c>
+      <c r="B217">
+        <v>89</v>
+      </c>
+      <c r="D217" s="11"/>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A218" s="11">
+        <v>39964</v>
+      </c>
+      <c r="B218">
+        <v>89.1</v>
+      </c>
+      <c r="D218" s="11"/>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A219" s="11">
+        <v>39933</v>
+      </c>
+      <c r="B219">
+        <v>89.2</v>
+      </c>
+      <c r="D219" s="11"/>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A220" s="11">
+        <v>39903</v>
+      </c>
+      <c r="B220">
+        <v>89.3</v>
+      </c>
+      <c r="D220" s="11"/>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A221" s="11">
+        <v>39872</v>
+      </c>
+      <c r="B221">
+        <v>89.4</v>
+      </c>
+      <c r="D221" s="11"/>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A222" s="11">
+        <v>39844</v>
+      </c>
+      <c r="B222">
+        <v>89.5</v>
+      </c>
+      <c r="D222" s="11"/>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A223" s="11">
+        <v>39813</v>
+      </c>
+      <c r="B223">
+        <v>89.4</v>
+      </c>
+      <c r="D223" s="11"/>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224" s="11">
+        <v>39782</v>
+      </c>
+      <c r="B224">
+        <v>89.4</v>
+      </c>
+      <c r="D224" s="11"/>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A225" s="11">
+        <v>39752</v>
+      </c>
+      <c r="B225">
+        <v>89.5</v>
+      </c>
+      <c r="D225" s="11"/>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A226" s="11">
+        <v>39721</v>
+      </c>
+      <c r="B226">
+        <v>89.3</v>
+      </c>
+      <c r="D226" s="11"/>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A227" s="11">
+        <v>39691</v>
+      </c>
+      <c r="B227">
+        <v>89.1</v>
+      </c>
+      <c r="D227" s="11"/>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A228" s="11">
+        <v>39660</v>
+      </c>
+      <c r="B228">
+        <v>88.9</v>
+      </c>
+      <c r="D228" s="11"/>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A229" s="11">
+        <v>39629</v>
+      </c>
+      <c r="B229">
+        <v>88.8</v>
+      </c>
+      <c r="D229" s="11"/>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A230" s="11">
+        <v>39599</v>
+      </c>
+      <c r="B230">
+        <v>88.6</v>
+      </c>
+      <c r="D230" s="11"/>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A231" s="11">
+        <v>39568</v>
+      </c>
+      <c r="B231">
+        <v>88.4</v>
+      </c>
+      <c r="D231" s="11"/>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A232" s="11">
+        <v>39538</v>
+      </c>
+      <c r="B232">
+        <v>88.2</v>
+      </c>
+      <c r="D232" s="11"/>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A233" s="11">
+        <v>39507</v>
+      </c>
+      <c r="B233">
+        <v>88.1</v>
+      </c>
+      <c r="D233" s="11"/>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A234" s="11">
+        <v>39478</v>
+      </c>
+      <c r="B234">
+        <v>88</v>
+      </c>
+      <c r="D234" s="11"/>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A235" s="11">
+        <v>39447</v>
+      </c>
+      <c r="B235">
+        <v>87.6</v>
+      </c>
+      <c r="D235" s="11"/>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A236" s="11">
+        <v>39416</v>
+      </c>
+      <c r="B236">
+        <v>87.3</v>
+      </c>
+      <c r="D236" s="11"/>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A237" s="11">
+        <v>39386</v>
+      </c>
+      <c r="B237">
+        <v>87.2</v>
+      </c>
+      <c r="D237" s="11"/>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A238" s="11">
+        <v>39355</v>
+      </c>
+      <c r="B238">
+        <v>87.3</v>
+      </c>
+      <c r="D238" s="11"/>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A239" s="11">
+        <v>39325</v>
+      </c>
+      <c r="B239">
+        <v>87.1</v>
+      </c>
+      <c r="D239" s="11"/>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A240" s="11">
+        <v>39294</v>
+      </c>
+      <c r="B240">
+        <v>87.1</v>
+      </c>
+      <c r="D240" s="11"/>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A241" s="11">
+        <v>39263</v>
+      </c>
+      <c r="B241">
+        <v>87</v>
+      </c>
+      <c r="D241" s="11"/>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A242" s="11">
+        <v>39233</v>
+      </c>
+      <c r="B242">
+        <v>87</v>
+      </c>
+      <c r="D242" s="11"/>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A243" s="11">
+        <v>39202</v>
+      </c>
+      <c r="B243">
+        <v>86.9</v>
+      </c>
+      <c r="D243" s="11"/>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A244" s="11">
+        <v>39172</v>
+      </c>
+      <c r="B244">
+        <v>86.9</v>
+      </c>
+      <c r="D244" s="11"/>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245" s="11">
+        <v>39141</v>
+      </c>
+      <c r="B245">
+        <v>86.7</v>
+      </c>
+      <c r="D245" s="11"/>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A246" s="11">
+        <v>39113</v>
+      </c>
+      <c r="B246">
+        <v>86.5</v>
+      </c>
+      <c r="D246" s="11"/>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A247" s="11">
+        <v>39082</v>
+      </c>
+      <c r="B247">
+        <v>85.8</v>
+      </c>
+      <c r="D247" s="11"/>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248" s="11">
+        <v>39051</v>
+      </c>
+      <c r="B248">
+        <v>85.9</v>
+      </c>
+      <c r="D248" s="11"/>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249" s="11">
+        <v>39021</v>
+      </c>
+      <c r="B249">
+        <v>85.8</v>
+      </c>
+      <c r="D249" s="11"/>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250" s="11">
+        <v>38990</v>
+      </c>
+      <c r="B250">
+        <v>85.7</v>
+      </c>
+      <c r="D250" s="11"/>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A251" s="11">
+        <v>38960</v>
+      </c>
+      <c r="B251">
+        <v>85.6</v>
+      </c>
+      <c r="D251" s="11"/>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252" s="11">
+        <v>38929</v>
+      </c>
+      <c r="B252">
+        <v>85.4</v>
+      </c>
+      <c r="D252" s="11"/>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A253" s="11">
+        <v>38898</v>
+      </c>
+      <c r="B253">
+        <v>85.2</v>
+      </c>
+      <c r="D253" s="11"/>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A254" s="11">
+        <v>38868</v>
+      </c>
+      <c r="B254">
+        <v>85.2</v>
+      </c>
+      <c r="D254" s="11"/>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A255" s="11">
+        <v>38837</v>
+      </c>
+      <c r="B255">
+        <v>85.2</v>
+      </c>
+      <c r="D255" s="11"/>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A256" s="11">
+        <v>38807</v>
+      </c>
+      <c r="B256">
+        <v>85.1</v>
+      </c>
+      <c r="D256" s="11"/>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A257" s="11">
+        <v>38776</v>
+      </c>
+      <c r="B257">
+        <v>84.8</v>
+      </c>
+      <c r="D257" s="11"/>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A258" s="11">
+        <v>38748</v>
+      </c>
+      <c r="B258">
+        <v>84.8</v>
+      </c>
+      <c r="D258" s="11"/>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A259" s="11">
+        <v>38717</v>
+      </c>
+      <c r="B259">
+        <v>84.5</v>
+      </c>
+      <c r="D259" s="11"/>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A260" s="11">
+        <v>38686</v>
+      </c>
+      <c r="B260">
+        <v>84.3</v>
+      </c>
+      <c r="D260" s="11"/>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A261" s="11">
+        <v>38656</v>
+      </c>
+      <c r="B261">
+        <v>84.4</v>
+      </c>
+      <c r="D261" s="11"/>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A262" s="11">
+        <v>38625</v>
+      </c>
+      <c r="B262">
+        <v>84.3</v>
+      </c>
+      <c r="D262" s="11"/>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A263" s="11">
+        <v>38595</v>
+      </c>
+      <c r="B263">
+        <v>84.4</v>
+      </c>
+      <c r="D263" s="11"/>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A264" s="11">
+        <v>38564</v>
+      </c>
+      <c r="B264">
+        <v>84.3</v>
+      </c>
+      <c r="D264" s="11"/>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A265" s="11">
+        <v>38533</v>
+      </c>
+      <c r="B265">
+        <v>84.3</v>
+      </c>
+      <c r="D265" s="11"/>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A266" s="11">
+        <v>38503</v>
+      </c>
+      <c r="B266">
+        <v>84.2</v>
+      </c>
+      <c r="D266" s="11"/>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A267" s="11">
+        <v>38472</v>
+      </c>
+      <c r="B267">
+        <v>84.1</v>
+      </c>
+      <c r="D267" s="11"/>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A268" s="11">
+        <v>38442</v>
+      </c>
+      <c r="B268">
+        <v>84.3</v>
+      </c>
+      <c r="D268" s="11"/>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A269" s="11">
+        <v>38411</v>
+      </c>
+      <c r="B269">
+        <v>83.9</v>
+      </c>
+      <c r="D269" s="11"/>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A270" s="11">
+        <v>38383</v>
+      </c>
+      <c r="B270">
+        <v>84.2</v>
+      </c>
+      <c r="D270" s="11"/>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A271" s="11">
+        <v>38352</v>
+      </c>
+      <c r="B271">
+        <v>83.8</v>
+      </c>
+      <c r="D271" s="11"/>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A272" s="11">
+        <v>38321</v>
+      </c>
+      <c r="B272">
+        <v>83.7</v>
+      </c>
+      <c r="D272" s="11"/>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A273" s="11">
+        <v>38291</v>
+      </c>
+      <c r="B273">
+        <v>83.7</v>
+      </c>
+      <c r="D273" s="11"/>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A274" s="11">
+        <v>38260</v>
+      </c>
+      <c r="B274">
+        <v>83.6</v>
+      </c>
+      <c r="D274" s="11"/>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A275" s="11">
+        <v>38230</v>
+      </c>
+      <c r="B275">
+        <v>83.5</v>
+      </c>
+      <c r="D275" s="11"/>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A276" s="11">
+        <v>38199</v>
+      </c>
+      <c r="B276">
+        <v>83.4</v>
+      </c>
+      <c r="D276" s="11"/>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A277" s="11">
+        <v>38168</v>
+      </c>
+      <c r="B277">
+        <v>83.3</v>
+      </c>
+      <c r="D277" s="11"/>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A278" s="11">
+        <v>38138</v>
+      </c>
+      <c r="B278">
+        <v>83.2</v>
+      </c>
+      <c r="D278" s="11"/>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A279" s="11">
+        <v>38107</v>
+      </c>
+      <c r="B279">
+        <v>83.1</v>
+      </c>
+      <c r="D279" s="11"/>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A280" s="11">
+        <v>38077</v>
+      </c>
+      <c r="B280">
+        <v>82.9</v>
+      </c>
+      <c r="D280" s="11"/>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A281" s="11">
+        <v>38046</v>
+      </c>
+      <c r="B281">
+        <v>82.9</v>
+      </c>
+      <c r="D281" s="11"/>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A282" s="11">
+        <v>38017</v>
+      </c>
+      <c r="B282">
+        <v>82.9</v>
+      </c>
+      <c r="D282" s="11"/>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A283" s="11">
+        <v>37986</v>
+      </c>
+      <c r="B283">
+        <v>82.9</v>
+      </c>
+      <c r="D283" s="11"/>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A284" s="11">
+        <v>37955</v>
+      </c>
+      <c r="B284">
+        <v>82.9</v>
+      </c>
+      <c r="D284" s="11"/>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A285" s="11">
+        <v>37925</v>
+      </c>
+      <c r="B285">
+        <v>82.9</v>
+      </c>
+      <c r="D285" s="11"/>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A286" s="11">
+        <v>37894</v>
+      </c>
+      <c r="B286">
+        <v>82.9</v>
+      </c>
+      <c r="D286" s="11"/>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A287" s="11">
+        <v>37864</v>
+      </c>
+      <c r="B287">
+        <v>82.9</v>
+      </c>
+      <c r="D287" s="11"/>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A288" s="11">
+        <v>37833</v>
+      </c>
+      <c r="B288">
+        <v>82.8</v>
+      </c>
+      <c r="D288" s="11"/>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A289" s="11">
+        <v>37802</v>
+      </c>
+      <c r="B289">
+        <v>82.8</v>
+      </c>
+      <c r="D289" s="11"/>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A290" s="11">
+        <v>37772</v>
+      </c>
+      <c r="B290">
+        <v>82.8</v>
+      </c>
+      <c r="D290" s="11"/>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A291" s="11">
+        <v>37741</v>
+      </c>
+      <c r="B291">
+        <v>82.8</v>
+      </c>
+      <c r="D291" s="11"/>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A292" s="11">
+        <v>37711</v>
+      </c>
+      <c r="B292">
+        <v>82.8</v>
+      </c>
+      <c r="D292" s="11"/>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A293" s="11">
+        <v>37680</v>
+      </c>
+      <c r="B293">
+        <v>82.7</v>
+      </c>
+      <c r="D293" s="11"/>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A294" s="11">
+        <v>37652</v>
+      </c>
+      <c r="B294">
+        <v>82.7</v>
+      </c>
+      <c r="D294" s="11"/>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A295" s="11">
+        <v>37621</v>
+      </c>
+      <c r="B295">
+        <v>82.7</v>
+      </c>
+      <c r="D295" s="11"/>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A296" s="11">
+        <v>37590</v>
+      </c>
+      <c r="B296">
+        <v>82.4</v>
+      </c>
+      <c r="D296" s="11"/>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A297" s="11">
+        <v>37560</v>
+      </c>
+      <c r="B297">
+        <v>82.5</v>
+      </c>
+      <c r="D297" s="11"/>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A298" s="11">
+        <v>37529</v>
+      </c>
+      <c r="B298">
+        <v>82.4</v>
+      </c>
+      <c r="D298" s="11"/>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A299" s="11">
+        <v>37499</v>
+      </c>
+      <c r="B299">
+        <v>82.4</v>
+      </c>
+      <c r="D299" s="11"/>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A300" s="11">
+        <v>37468</v>
+      </c>
+      <c r="B300">
+        <v>82.4</v>
+      </c>
+      <c r="D300" s="11"/>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A301" s="11">
+        <v>37437</v>
+      </c>
+      <c r="B301">
+        <v>82.3</v>
+      </c>
+      <c r="D301" s="11"/>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A302" s="11">
+        <v>37407</v>
+      </c>
+      <c r="B302">
+        <v>82.4</v>
+      </c>
+      <c r="D302" s="11"/>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A303" s="11">
+        <v>37376</v>
+      </c>
+      <c r="B303">
+        <v>82.3</v>
+      </c>
+      <c r="D303" s="11"/>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A304" s="11">
+        <v>37346</v>
+      </c>
+      <c r="B304">
+        <v>82.3</v>
+      </c>
+      <c r="D304" s="11"/>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A305" s="11">
+        <v>37315</v>
+      </c>
+      <c r="B305">
+        <v>82.3</v>
+      </c>
+      <c r="D305" s="11"/>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A306" s="11">
+        <v>37287</v>
+      </c>
+      <c r="B306">
+        <v>82.2</v>
+      </c>
+      <c r="D306" s="11"/>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A307" s="11">
+        <v>37256</v>
+      </c>
+      <c r="B307">
+        <v>81.8</v>
+      </c>
+      <c r="D307" s="11"/>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A308" s="11">
+        <v>37225</v>
+      </c>
+      <c r="B308">
+        <v>81.8</v>
+      </c>
+      <c r="D308" s="11"/>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A309" s="11">
+        <v>37195</v>
+      </c>
+      <c r="B309">
+        <v>81.8</v>
+      </c>
+      <c r="D309" s="11"/>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A310" s="11">
+        <v>37164</v>
+      </c>
+      <c r="B310">
+        <v>81.8</v>
+      </c>
+      <c r="D310" s="11"/>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A311" s="11">
+        <v>37134</v>
+      </c>
+      <c r="B311">
+        <v>81.7</v>
+      </c>
+      <c r="D311" s="11"/>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A312" s="11">
+        <v>37103</v>
+      </c>
+      <c r="B312">
+        <v>81.7</v>
+      </c>
+      <c r="D312" s="11"/>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A313" s="11">
+        <v>37072</v>
+      </c>
+      <c r="B313">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="D313" s="11"/>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A314" s="11">
+        <v>37042</v>
+      </c>
+      <c r="B314">
+        <v>81.5</v>
+      </c>
+      <c r="D314" s="11"/>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A315" s="11">
+        <v>37011</v>
+      </c>
+      <c r="B315">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="D315" s="11"/>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A316" s="11">
+        <v>36981</v>
+      </c>
+      <c r="B316">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="D316" s="11"/>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A317" s="11">
+        <v>36950</v>
+      </c>
+      <c r="B317">
+        <v>81.3</v>
+      </c>
+      <c r="D317" s="11"/>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A318" s="11">
+        <v>36922</v>
+      </c>
+      <c r="B318">
+        <v>81.2</v>
+      </c>
+      <c r="D318" s="11"/>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A319" s="11">
+        <v>36891</v>
+      </c>
+      <c r="B319">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="D319" s="11"/>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A320" s="11">
+        <v>36860</v>
+      </c>
+      <c r="B320">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="D320" s="11"/>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A321" s="11">
+        <v>36830</v>
+      </c>
+      <c r="B321">
+        <v>80.8</v>
+      </c>
+      <c r="D321" s="11"/>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A322" s="11">
+        <v>36799</v>
+      </c>
+      <c r="B322">
+        <v>80.7</v>
+      </c>
+      <c r="D322" s="11"/>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A323" s="11">
+        <v>36769</v>
+      </c>
+      <c r="B323">
+        <v>80.7</v>
+      </c>
+      <c r="D323" s="11"/>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A324" s="11">
+        <v>36738</v>
+      </c>
+      <c r="B324">
+        <v>80.8</v>
+      </c>
+      <c r="D324" s="11"/>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A325" s="11">
+        <v>36707</v>
+      </c>
+      <c r="B325">
+        <v>80.7</v>
+      </c>
+      <c r="D325" s="11"/>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A326" s="11">
+        <v>36677</v>
+      </c>
+      <c r="B326">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="D326" s="11"/>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A327" s="11">
+        <v>36646</v>
+      </c>
+      <c r="B327">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="D327" s="11"/>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A328" s="11">
+        <v>36616</v>
+      </c>
+      <c r="B328">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="D328" s="11"/>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A329" s="11">
+        <v>36585</v>
+      </c>
+      <c r="B329">
+        <v>80.5</v>
+      </c>
+      <c r="D329" s="11"/>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A330" s="11">
+        <v>36556</v>
+      </c>
+      <c r="B330">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="D330" s="11"/>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A331" s="11">
+        <v>36525</v>
+      </c>
+      <c r="B331">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="D331" s="11"/>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A332" s="11">
+        <v>36494</v>
+      </c>
+      <c r="B332">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="D332" s="11"/>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A333" s="11">
+        <v>36464</v>
+      </c>
+      <c r="B333">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="D333" s="11"/>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A334" s="11">
+        <v>36433</v>
+      </c>
+      <c r="B334">
+        <v>80.3</v>
+      </c>
+      <c r="D334" s="11"/>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A335" s="11">
+        <v>36403</v>
+      </c>
+      <c r="B335">
+        <v>80.3</v>
+      </c>
+      <c r="D335" s="11"/>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A336" s="11">
+        <v>36372</v>
+      </c>
+      <c r="B336">
+        <v>80.3</v>
+      </c>
+      <c r="D336" s="11"/>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A337" s="11">
+        <v>36341</v>
+      </c>
+      <c r="B337">
+        <v>80.3</v>
+      </c>
+      <c r="D337" s="11"/>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A338" s="11">
+        <v>36311</v>
+      </c>
+      <c r="B338">
+        <v>80.3</v>
+      </c>
+      <c r="D338" s="11"/>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A339" s="11">
+        <v>36280</v>
+      </c>
+      <c r="B339">
+        <v>80.3</v>
+      </c>
+      <c r="D339" s="11"/>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A340" s="11">
+        <v>36250</v>
+      </c>
+      <c r="B340">
+        <v>80.3</v>
+      </c>
+      <c r="D340" s="11"/>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A341" s="11">
+        <v>36219</v>
+      </c>
+      <c r="B341">
+        <v>80.2</v>
+      </c>
+      <c r="D341" s="11"/>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A342" s="11">
+        <v>36191</v>
+      </c>
+      <c r="B342">
+        <v>80.2</v>
+      </c>
+      <c r="D342" s="11"/>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A343" s="11">
+        <v>36160</v>
+      </c>
+      <c r="B343">
+        <v>80.3</v>
+      </c>
+      <c r="D343" s="11"/>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A344" s="11">
+        <v>36129</v>
+      </c>
+      <c r="B344">
+        <v>80.3</v>
+      </c>
+      <c r="D344" s="11"/>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A345" s="11">
+        <v>36099</v>
+      </c>
+      <c r="B345">
+        <v>80.3</v>
+      </c>
+      <c r="D345" s="11"/>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A346" s="11">
+        <v>36068</v>
+      </c>
+      <c r="B346">
+        <v>80.3</v>
+      </c>
+      <c r="D346" s="11"/>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A347" s="11">
+        <v>36038</v>
+      </c>
+      <c r="B347">
+        <v>80.2</v>
+      </c>
+      <c r="D347" s="11"/>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A348" s="11">
+        <v>36007</v>
+      </c>
+      <c r="B348">
+        <v>80.3</v>
+      </c>
+      <c r="D348" s="11"/>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A349" s="11">
+        <v>35976</v>
+      </c>
+      <c r="B349">
+        <v>80.3</v>
+      </c>
+      <c r="D349" s="11"/>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A350" s="11">
+        <v>35946</v>
+      </c>
+      <c r="B350">
+        <v>80.2</v>
+      </c>
+      <c r="D350" s="11"/>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A351" s="11">
+        <v>35915</v>
+      </c>
+      <c r="B351">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="D351" s="11"/>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A352" s="11">
+        <v>35885</v>
+      </c>
+      <c r="B352">
+        <v>80</v>
+      </c>
+      <c r="D352" s="11"/>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A353" s="11">
+        <v>35854</v>
+      </c>
+      <c r="B353">
+        <v>80</v>
+      </c>
+      <c r="D353" s="11"/>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A354" s="11">
+        <v>35826</v>
+      </c>
+      <c r="B354">
+        <v>80</v>
+      </c>
+      <c r="D354" s="11"/>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A355" s="11">
+        <v>35795</v>
+      </c>
+      <c r="B355">
+        <v>80</v>
+      </c>
+      <c r="D355" s="11"/>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A356" s="11">
+        <v>35764</v>
+      </c>
+      <c r="B356">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="D356" s="11"/>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A357" s="11">
+        <v>35734</v>
+      </c>
+      <c r="B357">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="D357" s="11"/>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A358" s="11">
+        <v>35703</v>
+      </c>
+      <c r="B358">
+        <v>80</v>
+      </c>
+      <c r="D358" s="11"/>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A359" s="11">
+        <v>35673</v>
+      </c>
+      <c r="B359">
+        <v>79.8</v>
+      </c>
+      <c r="D359" s="11"/>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A360" s="11">
+        <v>35642</v>
+      </c>
+      <c r="B360">
+        <v>79.8</v>
+      </c>
+      <c r="D360" s="11"/>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A361" s="11">
+        <v>35611</v>
+      </c>
+      <c r="B361">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="D361" s="11"/>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A362" s="11">
+        <v>35581</v>
+      </c>
+      <c r="B362">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="D362" s="11"/>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A363" s="11">
+        <v>35550</v>
+      </c>
+      <c r="B363">
+        <v>79.7</v>
+      </c>
+      <c r="D363" s="11"/>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A364" s="11">
+        <v>35520</v>
+      </c>
+      <c r="B364">
+        <v>79.7</v>
+      </c>
+      <c r="D364" s="11"/>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A365" s="11">
+        <v>35489</v>
+      </c>
+      <c r="B365">
+        <v>79.8</v>
+      </c>
+      <c r="D365" s="11"/>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A366" s="11">
+        <v>35461</v>
+      </c>
+      <c r="B366">
+        <v>79.7</v>
+      </c>
+      <c r="D366" s="11"/>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A367" s="11">
+        <v>35430</v>
+      </c>
+      <c r="B367">
+        <v>79.7</v>
+      </c>
+      <c r="D367" s="11"/>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A368" s="11">
+        <v>35399</v>
+      </c>
+      <c r="B368">
+        <v>79.7</v>
+      </c>
+      <c r="D368" s="11"/>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A369" s="11">
+        <v>35369</v>
+      </c>
+      <c r="B369">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="D369" s="11"/>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A370" s="11">
+        <v>35338</v>
+      </c>
+      <c r="B370">
+        <v>79.8</v>
+      </c>
+      <c r="D370" s="11"/>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A371" s="11">
+        <v>35308</v>
+      </c>
+      <c r="B371">
+        <v>79.7</v>
+      </c>
+      <c r="D371" s="11"/>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A372" s="11">
+        <v>35277</v>
+      </c>
+      <c r="B372">
+        <v>79.7</v>
+      </c>
+      <c r="D372" s="11"/>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A373" s="11">
+        <v>35246</v>
+      </c>
+      <c r="B373">
+        <v>79.7</v>
+      </c>
+      <c r="D373" s="11"/>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A374" s="11">
+        <v>35216</v>
+      </c>
+      <c r="B374">
+        <v>79.7</v>
+      </c>
+      <c r="D374" s="11"/>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A375" s="11">
+        <v>35185</v>
+      </c>
+      <c r="B375">
+        <v>79.7</v>
+      </c>
+      <c r="D375" s="11"/>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A376" s="11">
+        <v>35155</v>
+      </c>
+      <c r="B376">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="D376" s="11"/>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A377" s="11">
+        <v>35124</v>
+      </c>
+      <c r="B377">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="D377" s="11"/>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A378" s="11">
+        <v>35095</v>
+      </c>
+      <c r="B378">
+        <v>79.5</v>
+      </c>
+      <c r="D378" s="11"/>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A379" s="11">
+        <v>35064</v>
+      </c>
+      <c r="B379">
+        <v>79.2</v>
+      </c>
+      <c r="D379" s="11"/>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A380" s="11">
+        <v>35033</v>
+      </c>
+      <c r="B380">
+        <v>79.3</v>
+      </c>
+      <c r="D380" s="11"/>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A381" s="11">
+        <v>35003</v>
+      </c>
+      <c r="B381">
+        <v>79.2</v>
+      </c>
+      <c r="D381" s="11"/>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A382" s="11">
+        <v>34972</v>
+      </c>
+      <c r="B382">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="D382" s="11"/>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A383" s="11">
+        <v>34942</v>
+      </c>
+      <c r="B383">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="D383" s="11"/>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A384" s="11">
+        <v>34911</v>
+      </c>
+      <c r="B384">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="D384" s="11"/>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A385" s="11">
+        <v>34880</v>
+      </c>
+      <c r="B385">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="D385" s="11"/>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A386" s="11">
+        <v>34850</v>
+      </c>
+      <c r="B386">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="D386" s="11"/>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A387" s="11">
+        <v>34819</v>
+      </c>
+      <c r="B387">
+        <v>78.8</v>
+      </c>
+      <c r="D387" s="11"/>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A388" s="11">
+        <v>34789</v>
+      </c>
+      <c r="B388">
+        <v>78.8</v>
+      </c>
+      <c r="D388" s="11"/>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A389" s="11">
+        <v>34758</v>
+      </c>
+      <c r="B389">
+        <v>78.7</v>
+      </c>
+      <c r="D389" s="11"/>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A390" s="11">
+        <v>34730</v>
+      </c>
+      <c r="B390">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="D390" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -634,5 +4103,12 @@
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="B14:B15"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5818c103-b4ff-4ab6-8c05-dc2fb6993bc0}" enabled="0" method="" siteId="{5818c103-b4ff-4ab6-8c05-dc2fb6993bc0}" removed="1"/>
+</clbl:labelList>
 </file>